--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_la_araucania.xlsx
@@ -375,481 +375,481 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C2">
-        <v>230197</v>
+        <v>94.41793893129771</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C3">
-        <v>69440</v>
+        <v>93.97332551663492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C4">
-        <v>59461</v>
+        <v>93.93356368776504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C5">
-        <v>48926</v>
+        <v>93.7116912599319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="C6">
-        <v>37587</v>
+        <v>93.47025337649291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C7">
-        <v>32059</v>
+        <v>93.24062095730919</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C8">
-        <v>30717</v>
+        <v>93.18717586044319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C9">
-        <v>29671</v>
+        <v>92.92054557263477</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C10">
-        <v>26777</v>
+        <v>92.85519498227434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C11">
-        <v>24020</v>
+        <v>92.78723579241714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C12">
-        <v>23923</v>
+        <v>92.73951196057219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C13">
-        <v>23714</v>
+        <v>92.66632284682827</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C14">
-        <v>23145</v>
+        <v>92.48736511405545</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="C15">
-        <v>22378</v>
+        <v>92.33794089609151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C16">
-        <v>17968</v>
+        <v>92.31467348706737</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C17">
-        <v>17734</v>
+        <v>92.05137751303053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C18">
-        <v>16802</v>
+        <v>91.79091231806886</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C19">
-        <v>14415</v>
+        <v>91.64312463044477</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C20">
-        <v>13949</v>
+        <v>91.35511352831553</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C21">
-        <v>12384</v>
+        <v>91.28395544264217</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C22">
-        <v>11874</v>
+        <v>91.0604928072177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C23">
-        <v>11859</v>
+        <v>90.95806639487478</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C24">
-        <v>11282</v>
+        <v>90.64753406487399</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C25">
-        <v>10343</v>
+        <v>89.98857373302863</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C26">
-        <v>9890</v>
+        <v>89.72719361307655</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C27">
-        <v>9342</v>
+        <v>89.63809138697938</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C28">
-        <v>8584</v>
+        <v>88.78203434610303</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C29">
-        <v>8374</v>
+        <v>87.42813229350487</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C30">
-        <v>7749</v>
+        <v>87.41308086970584</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C31">
-        <v>6810</v>
+        <v>86.93015352162193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C32">
-        <v>6771</v>
+        <v>86.61615267499911</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C33">
-        <v>6247</v>
+        <v>78.95139384294573</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
